--- a/artfynd/A 59046-2022 artfynd.xlsx
+++ b/artfynd/A 59046-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59046-2022 artfynd.xlsx
+++ b/artfynd/A 59046-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105348064</v>
+        <v>119412117</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kylklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577361.2604997383</v>
+        <v>577361</v>
       </c>
       <c r="R2" t="n">
-        <v>7051188.838085042</v>
+        <v>7051188</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-12-26</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-12-26</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105357751</v>
+        <v>105348064</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577259.9476746869</v>
+        <v>577361</v>
       </c>
       <c r="R3" t="n">
-        <v>7051025.529317625</v>
+        <v>7051188</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,22 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110686312</v>
+        <v>105357751</v>
       </c>
       <c r="B4" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,38 +891,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kylbodarna, Ång</t>
+          <t>Kylklippen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577218.037427388</v>
+        <v>577260</v>
       </c>
       <c r="R4" t="n">
-        <v>7050950.992185705</v>
+        <v>7051025</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,27 +946,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,27 +966,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119412117</v>
+        <v>109012695</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,37 +989,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kylklippen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577361</v>
+        <v>577205</v>
       </c>
       <c r="R5" t="n">
-        <v>7051188</v>
+        <v>7050972</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,22 +1049,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,6 +1088,430 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>109012889</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kylbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>577205</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7050947</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>109242306</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kylbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>577160</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7051026</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-05-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-05-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>110686312</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kylbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>577218</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7050951</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>110686242</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kylbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577267</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7050884</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59046-2022 artfynd.xlsx
+++ b/artfynd/A 59046-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119412117</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105348064</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105357751</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109012695</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109012889</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109242306</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110686312</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,8 +1552,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110686242</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 59046-2022 artfynd.xlsx
+++ b/artfynd/A 59046-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1453,52 +1453,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110686242</v>
+        <v>135895610</v>
       </c>
       <c r="B9" t="n">
-        <v>98186</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220250</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kylbodarna, Ång</t>
+          <t>Kylbodarna, Kylbodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577267</v>
+        <v>577215</v>
       </c>
       <c r="R9" t="n">
-        <v>7050884</v>
+        <v>7051183</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1522,12 +1523,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,23 +1552,129 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135895610</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>110686242</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kylbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>577267</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7050884</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110686242</t>
         </is>
@@ -1568,6 +1690,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59046-2022 artfynd.xlsx
+++ b/artfynd/A 59046-2022 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>135895610</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 59046-2022 artfynd.xlsx
+++ b/artfynd/A 59046-2022 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>135895610</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 59046-2022 artfynd.xlsx
+++ b/artfynd/A 59046-2022 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>135895610</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 59046-2022 artfynd.xlsx
+++ b/artfynd/A 59046-2022 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>135895610</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 59046-2022 artfynd.xlsx
+++ b/artfynd/A 59046-2022 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>135895610</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 59046-2022 artfynd.xlsx
+++ b/artfynd/A 59046-2022 artfynd.xlsx
@@ -1456,7 +1456,7 @@
         <v>135895610</v>
       </c>
       <c r="B9" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
